--- a/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240126120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-A04-Loinc" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE-R308-TAASIP" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>

--- a/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240126120000</t>
+    <t>20240927120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -142,7 +142,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A04-Loinc/FHIR/TRE-A04-Loinc</t>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>MED-1278</t>
@@ -151,7 +151,7 @@
     <t>Lors d'un malaise</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R308-TAASIP/FHIR/TRE-R308-TAASIP</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
   </si>
 </sst>
 </file>
